--- a/tiflow-erezept/develop/2.0.0-ballot.2/ValueSet-tiflow-erezept-operation-outcome-details-vs.xlsx
+++ b/tiflow-erezept/develop/2.0.0-ballot.2/ValueSet-tiflow-erezept-operation-outcome-details-vs.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="105">
   <si>
     <t>Property</t>
   </si>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2028-04-01</t>
+    <t>2026-06-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -176,12 +176,6 @@
     <t>Task id required</t>
   </si>
   <si>
-    <t>TIFLOW_KVNR_MISMATCH</t>
-  </si>
-  <si>
-    <t>KVNR mismatch</t>
-  </si>
-  <si>
     <t>TIFLOW_SIGNATURE_INVALID_ISSUING_ROLE</t>
   </si>
   <si>
@@ -288,6 +282,30 @@
   </si>
   <si>
     <t>MVO not valid yet</t>
+  </si>
+  <si>
+    <t>TIFLOW_CONSENT_REQUIRED</t>
+  </si>
+  <si>
+    <t>Consent required</t>
+  </si>
+  <si>
+    <t>TIFLOW_ACCESS_PERMISSION_INVALID</t>
+  </si>
+  <si>
+    <t>Access permission invalid</t>
+  </si>
+  <si>
+    <t>TIFLOW_CONSENT_MISSING</t>
+  </si>
+  <si>
+    <t>Consent missing</t>
+  </si>
+  <si>
+    <t>TIFLOW_ACCESS_CODE_INVALID</t>
+  </si>
+  <si>
+    <t>Access code invalid</t>
   </si>
   <si>
     <t>https://gematik.de/fhir/tiflow/CodeSystem/tiflow-operation-outcome-details-cs</t>
@@ -617,7 +635,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -858,18 +876,42 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>31</v>
+        <v>91</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>31</v>
+        <v>92</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
         <v>32</v>
       </c>
-      <c r="B31" t="s" s="2">
-        <v>91</v>
+      <c r="B34" t="s" s="2">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -896,26 +938,26 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5">
@@ -931,7 +973,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
